--- a/data/trans_dic/IP31KM14_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 16,81</t>
+          <t>10,06; 28,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,54; 26,85</t>
+          <t>3,2; 16,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,49; 19,69</t>
+          <t>8,22; 19,45</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>13,43; 23,47</t>
+          <t>13,94; 23,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,82; 23,39</t>
+          <t>14,22; 24,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,94; 21,8</t>
+          <t>15,24; 22,08</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>19,55%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,93; 26,32</t>
+          <t>15,14; 26,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,33; 26,04</t>
+          <t>13,83; 24,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 24,34</t>
+          <t>16,18; 23,44</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,18; 21,95</t>
+          <t>13,35; 22,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13,92; 24,9</t>
+          <t>14,76; 24,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,44; 22,05</t>
+          <t>15,26; 21,75</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,39%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,53</t>
+          <t>16,12; 21,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,24; 22,69</t>
+          <t>15,42; 20,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16,22; 20,61</t>
+          <t>16,48; 20,37</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4102</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7803</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>10303</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1758; 7814</t>
+          <t>3765; 10695</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4322; 12161</t>
+          <t>1366; 7021</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7791; 18073</t>
+          <t>6588; 15579</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>28877</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>27569</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>56446</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21402; 37394</t>
+          <t>21894; 37496</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25139; 42556</t>
+          <t>20697; 35571</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>51001; 74408</t>
+          <t>46115; 66802</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>40632</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>77039</t>
+          <t>73278</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>25842; 45556</t>
+          <t>30300; 52330</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>32583; 55342</t>
+          <t>24152; 42544</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62906; 93841</t>
+          <t>60649; 87847</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>46628</t>
+          <t>51780</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>57315</t>
+          <t>48244</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103943</t>
+          <t>100024</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30653; 60205</t>
+          <t>39010; 65378</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42463; 75932</t>
+          <t>37683; 61438</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>83660; 127732</t>
+          <t>83566; 119068</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>157</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>114180</t>
+          <t>127855</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>141210</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>255390</t>
+          <t>240050</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>94435; 134058</t>
+          <t>110698; 148862</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>120956; 168997</t>
+          <t>95356; 129370</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>226784; 288156</t>
+          <t>215056; 265890</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM14_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan bollería industrial (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>17,54%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>8,76%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>10,06; 28,57</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3,2; 16,45</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,22; 19,45</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13,94; 23,88</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14,22; 24,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15,24; 22,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>20,3%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>18,69%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>19,55%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>15,14; 26,15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>13,83; 24,36</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>16,18; 23,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>13,35; 22,37</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>14,76; 24,06</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15,26; 21,75</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>18,62%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18,15%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>16,12; 21,67</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15,42; 20,93</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16,48; 20,37</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1754091965945215</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.08755145630110074</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1286040730272995</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10303</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.1005828255637792</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.03200081295621493</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.08223597921868314</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>3765; 10695</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1366; 7021</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6588; 15579</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.2856996410450754</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1645094811077068</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1944600488629233</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.1838795892064416</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.1894541619591673</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1865607089659978</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>28877</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>27569</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>56446</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.1394153055596707</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.1422329789254049</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.1524168410443907</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>21894; 37496</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>20697; 35571</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>46115; 66802</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.2387625863081597</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.2444431955316645</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.2207885488102888</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.2030334587105805</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1868945546422845</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.1955120249411466</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>40632</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>32645</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>73278</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1514036903056508</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.138272632952257</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.161816870861643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>30300; 52330</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>24152; 42544</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>60649; 87847</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2614835874704202</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.2435665468459838</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.2343839757834017</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.1771933776779583</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1889420232274663</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1826720041825789</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>51780</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>48244</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>100024</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1334953719427441</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.1475809383333214</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1526149095327505</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>39010; 65378</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>37683; 61438</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>83566; 119068</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.223728883059378</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.2406146528297937</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.21745320671112</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1861541793670633</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.181484130594831</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1839419260049512</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>127855</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>112195</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>240050</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1611731664784765</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.1542460378430545</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.1647899339923755</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>110698; 148862</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>95356; 129370</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>215056; 265890</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.216740078192304</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.209266430634316</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.2037425103976177</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan bollería industrial (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>6566</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3737</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>10303</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>3765</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1366</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6588</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>10695</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7021</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>15579</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>28877</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>27569</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>56446</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>21894</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>20697</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>37496</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>35571</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>66802</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>40632</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>32645</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>73278</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>30300</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>24152</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>60649</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>52330</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>42544</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>87847</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>51780</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>48244</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>100024</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>39010</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>37683</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>83566</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>65378</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>61438</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>119068</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>167</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>127855</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>112195</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>240050</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>110698</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>95356</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>215056</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>148862</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>129370</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>265890</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>